--- a/artifacts/literal-text-budget.xlsx
+++ b/artifacts/literal-text-budget.xlsx
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:39:14.360Z</t>
+          <t>2026-09-25T21:24:25.282Z</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
